--- a/etf_holdings/2026-09-01_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-09-01_active_etf_full_holdings_all.xlsx
@@ -486,17 +486,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -504,7 +504,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2330台灣積體</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -522,20 +522,20 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.19%3,800,000</t>
+          <t>9.38%11,014,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.19%</t>
+          <t>9.38%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3800000</v>
+        <v>11014000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -547,17 +547,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2383台光電子</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,16 +583,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.27%1,380,000</t>
+          <t>9.24%4,757,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.27%</t>
+          <t>9.24%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1380000</v>
+        <v>4757000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -608,17 +608,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2408南亞科技</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.56%543</t>
+          <t>+1.93%3425</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>543</v>
+        <v>3425</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9.18%13,800,000</t>
+          <t>7.21%5,949,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.18%</t>
+          <t>7.21%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>13800000</v>
+        <v>5949000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -669,17 +669,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2059川湖科技</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.84%14180</t>
+          <t>-10%999</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>14180</v>
+        <v>999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.68%500,000</t>
+          <t>7.18%20,300,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.68%</t>
+          <t>7.18%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>500000</v>
+        <v>20300000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -730,17 +730,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3037欣興電子</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-10%999</t>
+          <t>-1.51%3925</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>999</v>
+        <v>3925</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.12%5,000,000</t>
+          <t>7.07%5,088,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.12%</t>
+          <t>7.07%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5000000</v>
+        <v>5088000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -791,17 +791,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3017奇鋐科技</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.93%3425</t>
+          <t>-1.46%7095</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3425</v>
+        <v>7095</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.24%1,250,000</t>
+          <t>5.47%2,176,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.24%</t>
+          <t>5.47%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1250000</v>
+        <v>2176000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -852,17 +852,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6669緯穎科技</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.46%7095</t>
+          <t>+3.54%5990</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+3.54%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>7095</v>
+        <v>5990</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.04%580,000</t>
+          <t>5.08%2,397,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.04%</t>
+          <t>5.08%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>580000</v>
+        <v>2397000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -913,17 +913,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -931,7 +931,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2327國巨股份</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -949,20 +949,20 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.01%7,500,000</t>
+          <t>4.82%24,987,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>4.82%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7500000</v>
+        <v>24987000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -974,17 +974,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8046南亞電路</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.81%1230</t>
+          <t>+0.55%1840</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1230</v>
+        <v>1840</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.90%3,250,000</t>
+          <t>4.72%7,240,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>4.72%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3250000</v>
+        <v>7240000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1035,17 +1035,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2454聯發科技</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.51%3925</t>
+          <t>-4.24%2035</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-4.24%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3925</v>
+        <v>2035</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.33%900,000</t>
+          <t>4.66%6,464,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.66%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>900000</v>
+        <v>6464000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1096,17 +1096,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3189景碩科技</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-8.9%819</t>
+          <t>+1.99%5130</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>819</v>
+        <v>5130</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.11%4,100,000</t>
+          <t>4.50%2,476,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>4100000</v>
+        <v>2476000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1157,17 +1157,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.24%2035</t>
+          <t>-0.81%1230</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2035</v>
+        <v>1230</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.99%1,600,000</t>
+          <t>4.13%9,474,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>4.13%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1600000</v>
+        <v>9474000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1218,17 +1218,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3081聯亞光電</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+6.81%3530</t>
+          <t>-0.77%129</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+6.81%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3530</v>
+        <v>129</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.89%900,000</t>
+          <t>4.07%89,118,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>900000</v>
+        <v>89118000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1279,17 +1279,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6274台燿科技</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-3.69%1435</t>
+          <t>-5.96%584</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.69%</t>
+          <t>-5.96%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1435</v>
+        <v>584</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.52%2,000,000</t>
+          <t>3.86%18,679,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.86%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2000000</v>
+        <v>18679000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1340,17 +1340,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 03:30:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3653健策精密</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.54%5990</t>
+          <t>-3.98%2170</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+3.54%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5990</v>
+        <v>2170</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.49%340,000</t>
+          <t>3.53%4,591,848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>3.53%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>340000</v>
+        <v>4591848</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1401,17 +1401,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1419,40 +1419,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3026禾伸堂企</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0%742</t>
+          <t>-3.69%1435</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.69%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.45%2,700,000</t>
+          <t>2.74%5,398,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2700000</v>
+        <v>5398000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1464,17 +1464,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1482,40 +1482,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6223旺矽科技</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.99%5130</t>
+          <t>-1.71%2305</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>-1.71%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.39%380,000</t>
+          <t>1.41%1,731,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>380000</v>
+        <v>1731000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1527,17 +1527,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1565,20 +1565,20 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.37%120,500</t>
+          <t>1.18%207,900</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>120500</v>
+        <v>207900</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1590,17 +1590,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1608,40 +1608,40 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.7%2165</t>
+          <t>-4.81%257</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-4.81%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>257</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.33%880,000</t>
+          <t>1.17%12,818,450</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>880000</v>
+        <v>12818450</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1653,17 +1653,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1671,40 +1671,40 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>8210勤誠</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-9.71%5860</t>
+          <t>-2.12%969</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-9.71%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>969</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.15%300,000</t>
+          <t>0.83%2,427,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>300000</v>
+        <v>2427000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1716,17 +1716,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1734,40 +1734,40 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3711日月光投</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-5.96%584</t>
+          <t>+1.41%6100</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.96%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.01%9,000</t>
+          <t>0.70%325,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>9000</v>
+        <v>325000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1779,17 +1779,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1797,40 +1797,40 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3008大立光電</t>
+          <t>4979華星光</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+8.28%7650</t>
+          <t>-0.16%609</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+8.28%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>609</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>0.68%3,173,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>3173000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1842,17 +1842,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1860,40 +1860,40 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3044健鼎科技</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.33%496.5</t>
+          <t>+3.1%1165</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>496.5</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.60%1,457,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>1457000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1905,17 +1905,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1923,40 +1923,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.98%2170</t>
+          <t>-7.11%1175</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.98%</t>
+          <t>-7.11%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.54%1,300,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>1300000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1968,17 +1968,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1986,40 +1986,40 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3231緯創資通</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0%178</t>
+          <t>-2.98%228</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.98%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>228</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0.48%5,916,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>9000</v>
+        <v>5916000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2049,40 +2049,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3036文曄科技</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0%196</t>
+          <t>+6.16%2845</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+6.16%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.48%477,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>477000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2094,17 +2094,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -2112,40 +2112,40 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2412中華電信</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.37%136</t>
+          <t>+4.06%500</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+4.06%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>500</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.29%1,644,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>1644000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2157,17 +2157,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -2175,40 +2175,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.81%257</t>
+          <t>-0.99%199.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.81%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0%1,450</t>
+          <t>0.23%3,248,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1450</v>
+        <v>3248000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2220,17 +2220,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 03:30:58</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -2238,40 +2238,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1216統一企業</t>
+          <t>6271同欣電</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.66%76.2</t>
+          <t>-1.4%212</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>212</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.17%2,222,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>2222000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2283,17 +2283,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2301,38 +2301,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2404漢唐集成</t>
+          <t>3376新日興</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.4%1060</t>
+          <t>-1.38%214</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1060</v>
+        <v>214</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.13%1,740,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>1740000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2344,17 +2344,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2362,38 +2362,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2357華碩電腦</t>
+          <t>6191精成科</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+3.52%999</t>
+          <t>-1.18%83.7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+3.52%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>999</v>
+        <v>83.7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.12%3,988,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>3988000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2405,17 +2405,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2423,34 +2423,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.49%1960</t>
+          <t>+3.11%248.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+3.11%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1960</v>
+        <v>248.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.04%501,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>501000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2466,17 +2466,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2484,38 +2484,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2379瑞昱半導</t>
+          <t>2002中鋼</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.14%721</t>
+          <t>-0.52%18.95</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>721</v>
+        <v>18.95</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.03%5,163,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2527,17 +2527,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2545,25 +2545,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2382廣達電腦</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.8%338.5</t>
+          <t>-0.55%540</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>338.5</v>
+        <v>540</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2588,17 +2588,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2606,21 +2606,21 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2308台達電子</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.55%1840</t>
+          <t>+0.25%4075</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1840</v>
+        <v>4075</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2649,17 +2649,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2667,25 +2667,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2313華通電腦</t>
+          <t>2439美律</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+3.11%248.5</t>
+          <t>+0.38%78.8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+3.11%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>248.5</v>
+        <v>78.8</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0%1,253</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1253</v>
+        <v>1000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2710,17 +2710,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2728,25 +2728,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2317鴻海精密</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.19%250</t>
+          <t>+0.71%1425</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>250</v>
+        <v>1425</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2789,25 +2789,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2603長榮海運</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.86%233.5</t>
+          <t>+8.28%7650</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>+8.28%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>233.5</v>
+        <v>7650</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2832,17 +2832,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2850,25 +2850,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2880華南金融</t>
+          <t>2382廣達</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.73%41.35</t>
+          <t>+1.8%338.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.73%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>41.35</v>
+        <v>338.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0%9,090</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>9090</v>
+        <v>1000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2893,17 +2893,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2911,34 +2911,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2881富邦金融</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0%144</t>
+          <t>-1.47%1345</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>-1.47%</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1345</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0%8,000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="H41" t="n">
-        <v>144</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>0%9,000</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="K41" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2954,17 +2954,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2972,25 +2972,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2882國泰金融</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+4.74%110.5</t>
+          <t>+0.56%543</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+4.74%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>110.5</v>
+        <v>543</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -3015,17 +3015,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -3033,25 +3033,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2883凱基金融</t>
+          <t>2637慧洋-KY</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+3.36%33.85</t>
+          <t>+2.17%94.1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>33.85</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3076,17 +3076,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2884玉山金融</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+2.58%39.75</t>
+          <t>+0.56%6285</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>39.75</v>
+        <v>6285</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3137,17 +3137,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 03:31:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -3155,25 +3155,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2885元大金融</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+2.19%65.4</t>
+          <t>-2.49%1960</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+2.19%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>65.40000000000001</v>
+        <v>1960</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0%9,360</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9360</v>
+        <v>1000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3198,17 +3198,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:15</t>
+          <t>2026-09-01 03:31:01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -3216,27 +3216,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2886兆豐金融</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.73%48.55</t>
+          <t>-6.17%912</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.73%</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>48.55</t>
-        </is>
+          <t>-6.17%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>912</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3245,7 +3243,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3261,17 +3259,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:15</t>
+          <t>2026-09-01 03:31:01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -3279,27 +3277,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2887台新新光</t>
+          <t>4966譜瑞-KY</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+2.8%38.55</t>
+          <t>-1.03%578</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+2.8%</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>38.55</t>
-        </is>
+          <t>-1.03%</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>578</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3308,7 +3304,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3324,17 +3320,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:15</t>
+          <t>2026-09-01 03:31:01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -3342,27 +3338,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2890永豐金融</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+3.27%41.1</t>
+          <t>-1.55%89.1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+3.27%</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>41.1</t>
-        </is>
+          <t>-1.55%</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>89.09999999999999</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3371,7 +3365,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -3387,17 +3381,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:15</t>
+          <t>2026-09-01 03:31:01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -3405,27 +3399,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2891中國信託</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.47%64.7</t>
+          <t>-1.19%250</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.47%</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>64.7</t>
-        </is>
+          <t>-1.19%</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>250</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3434,7 +3426,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3450,17 +3442,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:15</t>
+          <t>2026-09-01 03:31:01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -3468,23 +3460,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2912統一超商</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.92%216.5</t>
+          <t>-0.98%151.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.92%</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>216.5</t>
-        </is>
+          <t>-0.98%</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>151.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3513,17 +3503,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:15</t>
+          <t>2026-09-01 03:31:01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -3531,27 +3521,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5347世界先進</t>
+          <t>2481強茂</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.98%151.5</t>
+          <t>-1.95%151</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.98%</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>151.5</t>
-        </is>
+          <t>-1.95%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>151</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%5,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3560,7 +3548,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3581,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3642,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3703,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3764,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3825,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3886,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3947,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4008,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4069,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4130,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4191,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4252,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4313,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4374,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4435,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:22</t>
+          <t>2026-09-01 03:32:06</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4496,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4557,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4618,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4679,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4740,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4801,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4862,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4923,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4984,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5045,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5106,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5167,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5228,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5289,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5350,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:23</t>
+          <t>2026-09-01 03:32:08</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5411,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5472,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5533,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5594,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5655,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5716,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5777,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5838,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5899,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5960,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6021,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6082,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6143,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6204,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6265,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:24</t>
+          <t>2026-09-01 03:32:09</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6326,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:26</t>
+          <t>2026-09-01 03:32:10</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6387,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:26</t>
+          <t>2026-09-01 03:32:10</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6448,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:26</t>
+          <t>2026-09-01 03:32:10</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6509,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:26</t>
+          <t>2026-09-01 03:32:10</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6570,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:26</t>
+          <t>2026-09-01 03:32:10</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6631,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6692,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6753,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6814,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6875,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6936,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6997,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7058,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7119,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7180,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7241,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7302,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7363,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7424,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7485,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7546,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7607,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7668,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7729,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7790,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7851,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7912,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7973,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8034,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8095,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8156,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8217,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8278,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8339,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8400,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8461,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8522,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8583,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8644,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8705,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8766,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8827,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8888,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8949,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9010,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9071,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9132,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9193,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9254,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9315,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9376,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9437,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9498,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9559,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9620,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9681,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9742,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9803,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9864,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9925,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9986,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10047,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10108,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10169,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10230,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10291,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10352,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10413,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10474,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10535,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10596,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10657,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10718,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10779,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10840,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10901,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10962,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:42</t>
+          <t>2026-09-01 03:32:25</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11023,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11084,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11145,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11206,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11267,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11328,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11389,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11450,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11511,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11572,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11633,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11694,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11755,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11816,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11877,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:43</t>
+          <t>2026-09-01 03:32:27</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11938,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11999,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12060,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12121,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12182,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12243,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12304,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12365,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12426,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12487,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12548,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12609,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12670,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12731,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12792,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:45</t>
+          <t>2026-09-01 03:32:28</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12853,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:46</t>
+          <t>2026-09-01 03:32:29</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12914,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:46</t>
+          <t>2026-09-01 03:32:29</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12975,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:46</t>
+          <t>2026-09-01 03:32:29</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13036,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:46</t>
+          <t>2026-09-01 03:32:29</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13097,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:46</t>
+          <t>2026-09-01 03:32:29</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13158,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:46</t>
+          <t>2026-09-01 03:32:29</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13219,7 +13207,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13280,7 +13268,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13341,7 +13329,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13402,7 +13390,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13463,7 +13451,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13524,7 +13512,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13585,7 +13573,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13646,7 +13634,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13707,7 +13695,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13768,7 +13756,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13829,7 +13817,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13890,7 +13878,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13951,7 +13939,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14012,7 +14000,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14073,7 +14061,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14134,7 +14122,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14195,7 +14183,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14256,7 +14244,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14317,7 +14305,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14378,7 +14366,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14439,7 +14427,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14500,7 +14488,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14561,7 +14549,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14622,7 +14610,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14683,7 +14671,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14744,7 +14732,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14805,7 +14793,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14866,7 +14854,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14927,7 +14915,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14988,7 +14976,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15049,7 +15037,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15110,7 +15098,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15171,7 +15159,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15232,7 +15220,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15293,7 +15281,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15354,7 +15342,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15415,7 +15403,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15476,7 +15464,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15537,7 +15525,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15598,7 +15586,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15659,7 +15647,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15720,7 +15708,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15781,7 +15769,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15842,7 +15830,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15903,7 +15891,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15964,7 +15952,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:57</t>
+          <t>2026-09-01 03:32:39</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16025,7 +16013,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:57</t>
+          <t>2026-09-01 03:32:39</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16086,7 +16074,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:57</t>
+          <t>2026-09-01 03:32:39</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16147,7 +16135,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:57</t>
+          <t>2026-09-01 03:32:39</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16208,7 +16196,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:57</t>
+          <t>2026-09-01 03:32:39</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16269,7 +16257,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16330,7 +16318,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16391,7 +16379,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16452,7 +16440,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16513,7 +16501,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16574,7 +16562,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16635,7 +16623,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16696,7 +16684,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16757,7 +16745,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16818,7 +16806,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16879,7 +16867,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16940,7 +16928,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -17001,7 +16989,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17062,7 +17050,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17123,7 +17111,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:03</t>
+          <t>2026-09-01 03:32:45</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17184,7 +17172,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17245,7 +17233,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17306,7 +17294,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17367,7 +17355,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17428,7 +17416,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17489,7 +17477,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17550,7 +17538,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17611,7 +17599,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17672,7 +17660,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17733,7 +17721,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17794,7 +17782,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17855,7 +17843,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17916,7 +17904,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17977,7 +17965,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18038,7 +18026,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:04</t>
+          <t>2026-09-01 03:32:46</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18099,7 +18087,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18160,7 +18148,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18221,7 +18209,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18282,7 +18270,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18343,7 +18331,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18404,7 +18392,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18465,7 +18453,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18526,7 +18514,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18587,7 +18575,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18648,7 +18636,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:05</t>
+          <t>2026-09-01 03:32:47</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18709,7 +18697,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:12</t>
+          <t>2026-09-01 03:32:54</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18772,7 +18760,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:12</t>
+          <t>2026-09-01 03:32:54</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18835,7 +18823,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:12</t>
+          <t>2026-09-01 03:32:54</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18898,7 +18886,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:12</t>
+          <t>2026-09-01 03:32:54</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18961,7 +18949,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:12</t>
+          <t>2026-09-01 03:32:54</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19024,7 +19012,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:13</t>
+          <t>2026-09-01 03:32:55</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19087,7 +19075,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:13</t>
+          <t>2026-09-01 03:32:55</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19150,7 +19138,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:13</t>
+          <t>2026-09-01 03:32:55</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19213,7 +19201,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:13</t>
+          <t>2026-09-01 03:32:55</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19276,7 +19264,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:14</t>
+          <t>2026-09-01 03:32:56</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19339,7 +19327,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:14</t>
+          <t>2026-09-01 03:32:56</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19402,7 +19390,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:14</t>
+          <t>2026-09-01 03:32:56</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19465,7 +19453,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:14</t>
+          <t>2026-09-01 03:32:56</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19528,7 +19516,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:14</t>
+          <t>2026-09-01 03:32:56</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19591,7 +19579,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:14</t>
+          <t>2026-09-01 03:32:56</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19654,7 +19642,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:16</t>
+          <t>2026-09-01 03:32:58</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19717,7 +19705,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19778,7 +19766,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19839,7 +19827,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19900,7 +19888,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19961,7 +19949,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -20022,7 +20010,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20083,7 +20071,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20144,7 +20132,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20205,7 +20193,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20266,7 +20254,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20327,7 +20315,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20388,7 +20376,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20449,7 +20437,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20510,7 +20498,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20571,7 +20559,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20632,7 +20620,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20693,7 +20681,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20754,7 +20742,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20815,7 +20803,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -20876,7 +20864,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -20937,7 +20925,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20998,7 +20986,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21059,7 +21047,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21120,7 +21108,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21181,7 +21169,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21242,7 +21230,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21303,7 +21291,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21364,7 +21352,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21425,7 +21413,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21486,7 +21474,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21547,7 +21535,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21608,7 +21596,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21669,7 +21657,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21730,7 +21718,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -21791,7 +21779,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -21852,7 +21840,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21913,7 +21901,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21974,7 +21962,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -22035,7 +22023,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22096,7 +22084,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22157,7 +22145,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22218,7 +22206,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22279,7 +22267,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22340,7 +22328,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22401,7 +22389,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22462,7 +22450,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:25</t>
+          <t>2026-09-01 03:33:08</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22523,7 +22511,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:25</t>
+          <t>2026-09-01 03:33:08</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22584,7 +22572,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:25</t>
+          <t>2026-09-01 03:33:08</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22645,7 +22633,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:25</t>
+          <t>2026-09-01 03:33:08</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22706,7 +22694,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:25</t>
+          <t>2026-09-01 03:33:08</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22767,7 +22755,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22828,7 +22816,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -22889,7 +22877,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -22950,7 +22938,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -23011,7 +22999,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -23072,7 +23060,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -23133,7 +23121,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -23194,7 +23182,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -23255,7 +23243,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -23316,7 +23304,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -23377,7 +23365,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -23438,7 +23426,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -23499,7 +23487,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -23560,7 +23548,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -23621,7 +23609,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:32</t>
+          <t>2026-09-01 03:33:14</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -23682,7 +23670,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -23743,7 +23731,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -23804,7 +23792,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -23865,7 +23853,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -23926,7 +23914,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -23987,7 +23975,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -24048,7 +24036,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -24109,7 +24097,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -24170,7 +24158,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -24231,7 +24219,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -24292,7 +24280,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -24353,7 +24341,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -24414,7 +24402,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -24475,7 +24463,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -24536,7 +24524,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:33</t>
+          <t>2026-09-01 03:33:15</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -24597,7 +24585,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -24658,7 +24646,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -24719,7 +24707,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -24780,7 +24768,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -24841,7 +24829,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -24902,7 +24890,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -24963,7 +24951,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -25024,7 +25012,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -25085,7 +25073,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -25146,7 +25134,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -25207,7 +25195,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -25268,7 +25256,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -25329,7 +25317,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -25390,7 +25378,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -25451,7 +25439,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:34</t>
+          <t>2026-09-01 03:33:17</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -25512,7 +25500,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:36</t>
+          <t>2026-09-01 03:33:18</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -25575,7 +25563,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:36</t>
+          <t>2026-09-01 03:33:18</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -25638,7 +25626,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:36</t>
+          <t>2026-09-01 03:33:18</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -25701,7 +25689,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:36</t>
+          <t>2026-09-01 03:33:18</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -25764,7 +25752,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:36</t>
+          <t>2026-09-01 03:33:18</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -25827,7 +25815,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -25888,7 +25876,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -25949,7 +25937,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -26010,7 +25998,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -26071,7 +26059,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -26132,7 +26120,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -26193,7 +26181,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -26254,7 +26242,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -26315,7 +26303,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -26376,7 +26364,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -26437,7 +26425,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -26498,7 +26486,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -26559,7 +26547,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -26620,7 +26608,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -26681,7 +26669,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:42</t>
+          <t>2026-09-01 03:33:25</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -26742,7 +26730,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -26805,7 +26793,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -26868,7 +26856,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -26931,7 +26919,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -26994,7 +26982,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -27057,7 +27045,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -27120,7 +27108,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -27183,7 +27171,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -27246,7 +27234,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -27309,7 +27297,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -27372,7 +27360,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -27435,7 +27423,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -27498,7 +27486,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -27561,7 +27549,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -27624,7 +27612,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:43</t>
+          <t>2026-09-01 03:33:26</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -27687,7 +27675,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -27748,7 +27736,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -27809,7 +27797,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -27870,7 +27858,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -27931,7 +27919,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -27992,7 +27980,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -28053,7 +28041,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -28114,7 +28102,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -28175,7 +28163,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -28236,7 +28224,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -28297,7 +28285,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -28358,7 +28346,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -28419,7 +28407,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -28480,7 +28468,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -28541,7 +28529,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:45</t>
+          <t>2026-09-01 03:33:27</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -28602,7 +28590,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:46</t>
+          <t>2026-09-01 03:33:29</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -28663,7 +28651,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:46</t>
+          <t>2026-09-01 03:33:29</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -28724,7 +28712,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:46</t>
+          <t>2026-09-01 03:33:29</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -28785,7 +28773,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:46</t>
+          <t>2026-09-01 03:33:29</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -28846,7 +28834,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:46</t>
+          <t>2026-09-01 03:33:29</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -28907,7 +28895,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:46</t>
+          <t>2026-09-01 03:33:29</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
